--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128465389</v>
+        <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>89357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,37 +926,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen NR, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346718</v>
+        <v>346621</v>
       </c>
       <c r="R4" t="n">
-        <v>6529597</v>
+        <v>6529617</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,24 +1010,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465389</t>
+          <t>https://artportalen.se/Sighting/137249626</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128465419</v>
+        <v>128465389</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1052,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346632</v>
+        <v>346718</v>
       </c>
       <c r="R5" t="n">
-        <v>6529633</v>
+        <v>6529597</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,38 +1123,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465419</t>
+          <t>https://artportalen.se/Sighting/128465389</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128465417</v>
+        <v>128465419</v>
       </c>
       <c r="B6" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346621</v>
+        <v>346632</v>
       </c>
       <c r="R6" t="n">
-        <v>6529622</v>
+        <v>6529633</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,53 +1225,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465417</t>
+          <t>https://artportalen.se/Sighting/128465419</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7069885</v>
+        <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93233</v>
+        <v>93115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dackehögen, Dls</t>
+          <t>Dackehögen NR, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346625</v>
+        <v>346616</v>
       </c>
       <c r="R7" t="n">
-        <v>6529630</v>
+        <v>6529625</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,12 +1296,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,34 +1320,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan  Olsson</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan  Olsson</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7069885</t>
+          <t>https://artportalen.se/Sighting/137249627</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112195875</v>
+        <v>128465417</v>
       </c>
       <c r="B8" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,37 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dackehögen, väster om NR, Dls</t>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346614</v>
+        <v>346621</v>
       </c>
       <c r="R8" t="n">
-        <v>6529634</v>
+        <v>6529622</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,12 +1408,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,36 +1422,30 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anita Stridvall, Jan  Olsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112195875</t>
+          <t>https://artportalen.se/Sighting/128465417</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128465390</v>
+        <v>7069885</v>
       </c>
       <c r="B9" t="n">
         <v>93233</v>
@@ -1465,17 +1476,16 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346741</v>
+        <v>346625</v>
       </c>
       <c r="R9" t="n">
-        <v>6529587</v>
+        <v>6529630</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1502,12 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,24 +1533,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Jan  Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Jan  Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465390</t>
+          <t>https://artportalen.se/Sighting/7069885</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128465391</v>
+        <v>112195875</v>
       </c>
       <c r="B10" t="n">
         <v>93233</v>
@@ -1569,22 +1579,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen, väster om NR, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346754</v>
+        <v>346614</v>
       </c>
       <c r="R10" t="n">
-        <v>6529578</v>
+        <v>6529634</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,12 +1615,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,27 +1633,32 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anita Stridvall, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465391</t>
+          <t>https://artportalen.se/Sighting/112195875</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128465393</v>
+        <v>128465390</v>
       </c>
       <c r="B11" t="n">
         <v>93233</v>
@@ -1684,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346765</v>
+        <v>346741</v>
       </c>
       <c r="R11" t="n">
-        <v>6529577</v>
+        <v>6529587</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,51 +1758,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128465393</t>
+          <t>https://artportalen.se/Sighting/128465390</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128465418</v>
+        <v>128465391</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346633</v>
+        <v>346754</v>
       </c>
       <c r="R12" t="n">
-        <v>6529629</v>
+        <v>6529578</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1831,6 +1846,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,6 +1863,214 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465391</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128465393</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>346765</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6529577</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465393</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128465418</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>346633</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6529629</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128465418</t>
         </is>
@@ -1865,6 +2089,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89357</v>
+        <v>89360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89360</v>
+        <v>89370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89370</v>
+        <v>89371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89371</v>
+        <v>89374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89374</v>
+        <v>89379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89379</v>
+        <v>89390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>137249626</v>
       </c>
       <c r="B4" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>137249627</v>
       </c>
       <c r="B7" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
